--- a/fichier_tests/journal_banque.xlsx
+++ b/fichier_tests/journal_banque.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ELITE BOOK\DSI_2025\001_projet_perso\rapp_bancaire\fichier_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928E0C84-C401-4861-8999-0D9FFAB56883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47DE4C0-B776-4336-90C6-242768A39D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{11924B93-9C9A-41AF-8080-AD131770AA0B}"/>
   </bookViews>
@@ -229,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,6 +295,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -353,18 +384,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -401,6 +426,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -727,28 +764,28 @@
     <col min="3" max="3" width="38.5546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="14" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="10" customWidth="1"/>
     <col min="7" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="23" customFormat="1" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="1" spans="1:6" s="21" customFormat="1" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:6" s="26" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -756,217 +793,217 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>45931</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10">
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>18960597</v>
       </c>
     </row>
     <row r="4" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
+      <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <v>45936</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18">
+      <c r="D4" s="15"/>
+      <c r="E4" s="16">
         <v>767000</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="17">
         <f>+F3+D4-E4</f>
         <v>18193597</v>
       </c>
     </row>
     <row r="5" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="13">
         <v>45936</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="20">
+      <c r="D5" s="15"/>
+      <c r="E5" s="18">
         <v>2149000</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="17">
         <f t="shared" ref="F5:F58" si="0">+F4+D5-E5</f>
         <v>16044597</v>
       </c>
     </row>
     <row r="6" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="13">
         <v>45936</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18">
+      <c r="D6" s="15"/>
+      <c r="E6" s="16">
         <v>562800</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="17">
         <f t="shared" si="0"/>
         <v>15481797</v>
       </c>
     </row>
     <row r="7" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="12">
         <v>5</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="13">
         <v>45937</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18">
+      <c r="D7" s="15"/>
+      <c r="E7" s="16">
         <v>574000</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="17">
         <f t="shared" si="0"/>
         <v>14907797</v>
       </c>
     </row>
     <row r="8" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="A8" s="12">
         <v>6</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="13">
         <v>45938</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18">
+      <c r="D8" s="15"/>
+      <c r="E8" s="16">
         <v>608000</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="17">
         <f t="shared" si="0"/>
         <v>14299797</v>
       </c>
     </row>
     <row r="9" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="12">
         <v>7</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="13">
         <v>45938</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18">
+      <c r="D9" s="15"/>
+      <c r="E9" s="16">
         <v>216000</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="17">
         <f t="shared" si="0"/>
         <v>14083797</v>
       </c>
     </row>
     <row r="10" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="12">
         <v>8</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="13">
         <v>45939</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18">
+      <c r="D10" s="15"/>
+      <c r="E10" s="16">
         <v>650300</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="17">
         <f t="shared" si="0"/>
         <v>13433497</v>
       </c>
     </row>
     <row r="11" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="12">
         <v>9</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="13">
         <v>45939</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18">
+      <c r="D11" s="15"/>
+      <c r="E11" s="16">
         <v>320000</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="17">
         <f t="shared" si="0"/>
         <v>13113497</v>
       </c>
     </row>
     <row r="12" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13">
         <v>45943</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18">
+      <c r="D12" s="15"/>
+      <c r="E12" s="16">
         <v>451000</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="17">
         <f t="shared" si="0"/>
         <v>12662497</v>
       </c>
     </row>
     <row r="13" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13">
         <v>45943</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18">
+      <c r="D13" s="15"/>
+      <c r="E13" s="16">
         <v>200000</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>12462497</v>
       </c>
     </row>
     <row r="14" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13">
         <v>45953</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="15">
         <v>1400</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19">
+      <c r="E14" s="16"/>
+      <c r="F14" s="17">
         <f t="shared" si="0"/>
         <v>12463897</v>
       </c>
@@ -975,17 +1012,17 @@
       <c r="A15" s="3">
         <v>2</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>45971</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9">
+      <c r="D15" s="6"/>
+      <c r="E15" s="7">
         <v>277000</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="17">
         <f t="shared" si="0"/>
         <v>12186897</v>
       </c>
@@ -994,17 +1031,17 @@
       <c r="A16" s="3">
         <v>3</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>45971</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9">
+      <c r="D16" s="6"/>
+      <c r="E16" s="7">
         <v>230000</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="17">
         <f t="shared" si="0"/>
         <v>11956897</v>
       </c>
@@ -1013,17 +1050,17 @@
       <c r="A17" s="3">
         <v>4</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>45971</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="9">
+      <c r="D17" s="6"/>
+      <c r="E17" s="7">
         <v>350000</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="17">
         <f t="shared" si="0"/>
         <v>11606897</v>
       </c>
@@ -1032,17 +1069,17 @@
       <c r="A18" s="3">
         <v>5</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>45971</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9">
+      <c r="D18" s="6"/>
+      <c r="E18" s="7">
         <v>259000</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="17">
         <f t="shared" si="0"/>
         <v>11347897</v>
       </c>
@@ -1051,17 +1088,17 @@
       <c r="A19" s="3">
         <v>6</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>45971</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="9">
+      <c r="D19" s="6"/>
+      <c r="E19" s="7">
         <v>350000</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="17">
         <f t="shared" si="0"/>
         <v>10997897</v>
       </c>
@@ -1070,17 +1107,17 @@
       <c r="A20" s="3">
         <v>7</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>45971</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9">
+      <c r="D20" s="6"/>
+      <c r="E20" s="7">
         <v>280000</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="17">
         <f t="shared" si="0"/>
         <v>10717897</v>
       </c>
@@ -1089,737 +1126,738 @@
       <c r="A21" s="3">
         <v>8</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>45972</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="21">
-        <v>820000</v>
-      </c>
-      <c r="F21" s="19">
-        <f t="shared" si="0"/>
-        <v>9897897</v>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7">
+        <v>280000</v>
+      </c>
+      <c r="F21" s="17">
+        <f t="shared" si="0"/>
+        <v>10437897</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>9</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="5">
         <v>45972</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="9">
+      <c r="D22" s="6"/>
+      <c r="E22" s="7">
         <v>349000</v>
       </c>
-      <c r="F22" s="19">
-        <f t="shared" si="0"/>
-        <v>9548897</v>
+      <c r="F22" s="17">
+        <f t="shared" si="0"/>
+        <v>10088897</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>10</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="5">
         <v>45972</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="9">
+      <c r="D23" s="6"/>
+      <c r="E23" s="7">
         <v>136000</v>
       </c>
-      <c r="F23" s="19">
-        <f t="shared" si="0"/>
-        <v>9412897</v>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>9952897</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>11</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="5">
         <v>45973</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="9">
+      <c r="D24" s="6"/>
+      <c r="E24" s="7">
         <v>76000</v>
       </c>
-      <c r="F24" s="19">
-        <f t="shared" si="0"/>
-        <v>9336897</v>
+      <c r="F24" s="17">
+        <f t="shared" si="0"/>
+        <v>9876897</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>12</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="5">
         <v>45973</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="9">
+      <c r="D25" s="6"/>
+      <c r="E25" s="7">
         <v>182000</v>
       </c>
-      <c r="F25" s="19">
-        <f t="shared" si="0"/>
-        <v>9154897</v>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
+        <v>9694897</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>13</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="5">
         <v>45973</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="9">
+      <c r="D26" s="6"/>
+      <c r="E26" s="7">
         <v>139000</v>
       </c>
-      <c r="F26" s="19">
-        <f t="shared" si="0"/>
-        <v>9015897</v>
+      <c r="F26" s="17">
+        <f t="shared" si="0"/>
+        <v>9555897</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>14</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="5">
         <v>45973</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="9">
+      <c r="D27" s="6"/>
+      <c r="E27" s="7">
         <v>349000</v>
       </c>
-      <c r="F27" s="19">
-        <f t="shared" si="0"/>
-        <v>8666897</v>
+      <c r="F27" s="17">
+        <f t="shared" si="0"/>
+        <v>9206897</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>15</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="5">
         <v>45973</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="9">
+      <c r="D28" s="6"/>
+      <c r="E28" s="7">
         <v>349000</v>
       </c>
-      <c r="F28" s="19">
-        <f t="shared" si="0"/>
-        <v>8317897</v>
+      <c r="F28" s="17">
+        <f t="shared" si="0"/>
+        <v>8857897</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>16</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="5">
         <v>45974</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="9">
+      <c r="D29" s="6"/>
+      <c r="E29" s="7">
         <v>389500</v>
       </c>
-      <c r="F29" s="19">
-        <f t="shared" si="0"/>
-        <v>7928397</v>
+      <c r="F29" s="17">
+        <f t="shared" si="0"/>
+        <v>8468397</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>17</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="5">
         <v>45974</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="9">
+      <c r="D30" s="6"/>
+      <c r="E30" s="7">
         <v>392500</v>
       </c>
-      <c r="F30" s="19">
-        <f t="shared" si="0"/>
-        <v>7535897</v>
+      <c r="F30" s="17">
+        <f t="shared" si="0"/>
+        <v>8075897</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>18</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="5">
         <v>45974</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="9">
+      <c r="D31" s="6"/>
+      <c r="E31" s="7">
         <v>385000</v>
       </c>
-      <c r="F31" s="19">
-        <f t="shared" si="0"/>
-        <v>7150897</v>
+      <c r="F31" s="17">
+        <f t="shared" si="0"/>
+        <v>7690897</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>19</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="5">
         <v>45974</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="9">
+      <c r="D32" s="6"/>
+      <c r="E32" s="7">
         <v>229000</v>
       </c>
-      <c r="F32" s="19">
-        <f t="shared" si="0"/>
-        <v>6921897</v>
+      <c r="F32" s="17">
+        <f t="shared" si="0"/>
+        <v>7461897</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>20</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="5">
         <v>45975</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="9">
+      <c r="D33" s="6"/>
+      <c r="E33" s="7">
         <v>238500</v>
       </c>
-      <c r="F33" s="19">
-        <f t="shared" si="0"/>
-        <v>6683397</v>
+      <c r="F33" s="17">
+        <f t="shared" si="0"/>
+        <v>7223397</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>21</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="5">
         <v>45975</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="9">
+      <c r="D34" s="6"/>
+      <c r="E34" s="7">
         <v>225000</v>
       </c>
-      <c r="F34" s="19">
-        <f t="shared" si="0"/>
-        <v>6458397</v>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
+        <v>6998397</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>22</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="5">
         <v>45978</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="9">
+      <c r="D35" s="6"/>
+      <c r="E35" s="7">
         <v>385000</v>
       </c>
-      <c r="F35" s="19">
-        <f t="shared" si="0"/>
-        <v>6073397</v>
+      <c r="F35" s="17">
+        <f t="shared" si="0"/>
+        <v>6613397</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>23</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="5">
         <v>45978</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="9">
+      <c r="D36" s="6"/>
+      <c r="E36" s="7">
         <v>400000</v>
       </c>
-      <c r="F36" s="19">
-        <f t="shared" si="0"/>
-        <v>5673397</v>
+      <c r="F36" s="17">
+        <f t="shared" si="0"/>
+        <v>6213397</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>24</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="5">
         <v>45978</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="9">
+      <c r="D37" s="6"/>
+      <c r="E37" s="7">
         <v>229000</v>
       </c>
-      <c r="F37" s="19">
-        <f t="shared" si="0"/>
-        <v>5444397</v>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>5984397</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>25</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="5">
         <v>45978</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="9">
+      <c r="D38" s="6"/>
+      <c r="E38" s="7">
         <v>352500</v>
       </c>
-      <c r="F38" s="19">
-        <f t="shared" si="0"/>
-        <v>5091897</v>
+      <c r="F38" s="17">
+        <f t="shared" si="0"/>
+        <v>5631897</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>26</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="5">
         <v>45978</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="9">
+      <c r="D39" s="6"/>
+      <c r="E39" s="7">
         <v>390000</v>
       </c>
-      <c r="F39" s="19">
-        <f t="shared" si="0"/>
-        <v>4701897</v>
+      <c r="F39" s="17">
+        <f t="shared" si="0"/>
+        <v>5241897</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>27</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>45978</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="9">
+      <c r="D40" s="6"/>
+      <c r="E40" s="7">
         <v>139000</v>
       </c>
-      <c r="F40" s="19">
-        <f t="shared" si="0"/>
-        <v>4562897</v>
+      <c r="F40" s="17">
+        <f t="shared" si="0"/>
+        <v>5102897</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>28</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="5">
         <v>45979</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="9">
+      <c r="D41" s="6"/>
+      <c r="E41" s="7">
         <v>77000</v>
       </c>
-      <c r="F41" s="19">
-        <f t="shared" si="0"/>
-        <v>4485897</v>
+      <c r="F41" s="17">
+        <f t="shared" si="0"/>
+        <v>5025897</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>29</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="5">
         <v>45979</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="21">
+      <c r="D42" s="6"/>
+      <c r="E42" s="19">
         <v>232500</v>
       </c>
-      <c r="F42" s="19">
-        <f t="shared" si="0"/>
-        <v>4253397</v>
+      <c r="F42" s="17">
+        <f t="shared" si="0"/>
+        <v>4793397</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>30</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="5">
         <v>45979</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="9">
+      <c r="D43" s="6"/>
+      <c r="E43" s="7">
         <v>229000</v>
       </c>
-      <c r="F43" s="19">
-        <f t="shared" si="0"/>
-        <v>4024397</v>
+      <c r="F43" s="17">
+        <f t="shared" si="0"/>
+        <v>4564397</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>31</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="5">
         <v>45979</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="9">
+      <c r="D44" s="6"/>
+      <c r="E44" s="7">
         <v>349000</v>
       </c>
-      <c r="F44" s="19">
-        <f t="shared" si="0"/>
-        <v>3675397</v>
+      <c r="F44" s="17">
+        <f t="shared" si="0"/>
+        <v>4215397</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>32</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="5">
         <v>45979</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="9">
+      <c r="D45" s="6"/>
+      <c r="E45" s="7">
         <v>277000</v>
       </c>
-      <c r="F45" s="19">
-        <f t="shared" si="0"/>
-        <v>3398397</v>
+      <c r="F45" s="17">
+        <f t="shared" si="0"/>
+        <v>3938397</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>33</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="5">
         <v>45980</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="9">
+      <c r="D46" s="6"/>
+      <c r="E46" s="7">
         <v>202000</v>
       </c>
-      <c r="F46" s="19">
-        <f t="shared" si="0"/>
-        <v>3196397</v>
+      <c r="F46" s="17">
+        <f t="shared" si="0"/>
+        <v>3736397</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>34</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="5">
         <v>45981</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="9">
+      <c r="D47" s="6"/>
+      <c r="E47" s="7">
         <v>322500</v>
       </c>
-      <c r="F47" s="19">
-        <f t="shared" si="0"/>
-        <v>2873897</v>
+      <c r="F47" s="17">
+        <f t="shared" si="0"/>
+        <v>3413897</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>35</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="5">
         <v>45981</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="9">
+      <c r="D48" s="6"/>
+      <c r="E48" s="7">
         <v>51000</v>
       </c>
-      <c r="F48" s="19">
-        <f t="shared" si="0"/>
-        <v>2822897</v>
+      <c r="F48" s="17">
+        <f t="shared" si="0"/>
+        <v>3362897</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>36</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="5">
         <v>45982</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="21">
-        <v>532500</v>
-      </c>
-      <c r="F49" s="19">
-        <f t="shared" si="0"/>
-        <v>2290397</v>
+      <c r="D49" s="6"/>
+      <c r="E49" s="27">
+        <v>352500</v>
+      </c>
+      <c r="F49" s="17">
+        <f t="shared" si="0"/>
+        <v>3010397</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>37</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="5">
         <v>45982</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="20">
         <v>9100</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="19">
-        <f t="shared" si="0"/>
-        <v>2299497</v>
+      <c r="E50" s="7"/>
+      <c r="F50" s="17">
+        <f t="shared" si="0"/>
+        <v>3019497</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>38</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="5">
         <v>45985</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="9">
+      <c r="D51" s="6"/>
+      <c r="E51" s="7">
         <v>319000</v>
       </c>
-      <c r="F51" s="19">
-        <f t="shared" si="0"/>
-        <v>1980497</v>
+      <c r="F51" s="17">
+        <f t="shared" si="0"/>
+        <v>2700497</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>39</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="5">
         <v>45985</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="8"/>
-      <c r="E52" s="9">
+      <c r="D52" s="6"/>
+      <c r="E52" s="7">
         <v>349000</v>
       </c>
-      <c r="F52" s="19">
-        <f t="shared" si="0"/>
-        <v>1631497</v>
+      <c r="F52" s="17">
+        <f t="shared" si="0"/>
+        <v>2351497</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>40</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="5">
         <v>45985</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="9">
+      <c r="D53" s="6"/>
+      <c r="E53" s="7">
         <v>448000</v>
       </c>
-      <c r="F53" s="19">
-        <f t="shared" si="0"/>
-        <v>1183497</v>
+      <c r="F53" s="17">
+        <f t="shared" si="0"/>
+        <v>1903497</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>41</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="5">
         <v>45985</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="21">
+      <c r="D54" s="6"/>
+      <c r="E54" s="19">
         <v>513000</v>
       </c>
-      <c r="F54" s="19">
-        <f t="shared" si="0"/>
-        <v>670497</v>
+      <c r="F54" s="17">
+        <f t="shared" si="0"/>
+        <v>1390497</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>42</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="5">
         <v>45986</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="9">
+      <c r="D55" s="6"/>
+      <c r="E55" s="7">
         <v>227000</v>
       </c>
-      <c r="F55" s="19">
-        <f t="shared" si="0"/>
-        <v>443497</v>
+      <c r="F55" s="17">
+        <f t="shared" si="0"/>
+        <v>1163497</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>43</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="5">
         <v>45987</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="9">
+      <c r="D56" s="6"/>
+      <c r="E56" s="7">
         <v>77000</v>
       </c>
-      <c r="F56" s="19">
-        <f t="shared" si="0"/>
-        <v>366497</v>
+      <c r="F56" s="17">
+        <f t="shared" si="0"/>
+        <v>1086497</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>44</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="5">
         <v>45987</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="9">
+      <c r="D57" s="6"/>
+      <c r="E57" s="7">
         <v>406000</v>
       </c>
-      <c r="F57" s="19">
-        <f t="shared" si="0"/>
-        <v>-39503</v>
+      <c r="F57" s="17">
+        <f t="shared" si="0"/>
+        <v>680497</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>45</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="5">
         <v>45988</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="21">
-        <v>838000</v>
-      </c>
-      <c r="F58" s="19">
-        <f t="shared" si="0"/>
-        <v>-877503</v>
+      <c r="D58" s="6"/>
+      <c r="E58" s="7">
+        <v>388000</v>
+      </c>
+      <c r="F58" s="17">
+        <f t="shared" si="0"/>
+        <v>292497</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="13"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="11"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:XFD1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>